--- a/Data/EXCEL/Transfer/salemon/202206/6763-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6763-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77521ED5-CCD5-41D2-880B-D39EDB6FD0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70D93376-D87B-475C-AE6C-B5CFC5EE1C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6763-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,19 +1218,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="7" width="10.625" customWidth="1"/>
-    <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
-    <col min="14" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="11.125" customWidth="1"/>
-    <col min="17" max="17" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="7" width="12.125" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+    <col min="9" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
+    <col min="12" max="12" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="12.75" customWidth="1"/>
+    <col min="14" max="15" width="12.125" customWidth="1"/>
+    <col min="16" max="16" width="12.75" customWidth="1"/>
+    <col min="17" max="17" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1383,219 +1383,219 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>509</v>
+        <v>573</v>
       </c>
       <c r="C5" s="7">
-        <v>566</v>
+        <v>429</v>
       </c>
       <c r="D5" s="7">
-        <v>624</v>
+        <v>587</v>
       </c>
       <c r="E5" s="7">
-        <v>497</v>
+        <v>429</v>
       </c>
       <c r="F5" s="8">
-        <v>57</v>
+        <v>-137</v>
       </c>
       <c r="G5" s="8">
-        <v>11.2</v>
+        <v>-24.2</v>
       </c>
       <c r="H5" s="9">
-        <v>1.26</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I5" s="8">
-        <v>10.3</v>
+        <v>-7.85</v>
       </c>
       <c r="J5" s="8">
-        <v>3.54</v>
+        <v>-10.3</v>
       </c>
       <c r="K5" s="9">
-        <v>5.97</v>
-      </c>
-      <c r="L5" s="8">
-        <v>12</v>
+        <v>7.14</v>
+      </c>
+      <c r="L5" s="10">
+        <v>7.63</v>
       </c>
       <c r="M5" s="9">
-        <v>1.26</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="N5" s="8">
-        <v>10.3</v>
+        <v>-7.85</v>
       </c>
       <c r="O5" s="8">
-        <v>3.54</v>
+        <v>-10.3</v>
       </c>
       <c r="P5" s="9">
-        <v>5.97</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>12</v>
+        <v>7.14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>7.63</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>700</v>
+        <v>509</v>
       </c>
       <c r="C6" s="7">
-        <v>509</v>
+        <v>566</v>
       </c>
       <c r="D6" s="7">
-        <v>700</v>
+        <v>624</v>
       </c>
       <c r="E6" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F6" s="10">
-        <v>-195</v>
+        <v>57</v>
       </c>
       <c r="G6" s="10">
-        <v>-27.7</v>
+        <v>11.2</v>
       </c>
       <c r="H6" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="I6" s="10">
-        <v>-10.8</v>
-      </c>
-      <c r="J6" s="8">
-        <v>13.2</v>
+        <v>10.3</v>
+      </c>
+      <c r="J6" s="10">
+        <v>3.54</v>
       </c>
       <c r="K6" s="9">
-        <v>4.71</v>
-      </c>
-      <c r="L6" s="8">
-        <v>14.5</v>
+        <v>5.97</v>
+      </c>
+      <c r="L6" s="10">
+        <v>12</v>
       </c>
       <c r="M6" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="N6" s="10">
-        <v>-10.8</v>
-      </c>
-      <c r="O6" s="8">
-        <v>13.2</v>
+        <v>10.3</v>
+      </c>
+      <c r="O6" s="10">
+        <v>3.54</v>
       </c>
       <c r="P6" s="9">
-        <v>4.71</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>14.5</v>
+        <v>5.97</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>831</v>
+        <v>700</v>
       </c>
       <c r="C7" s="7">
-        <v>704</v>
+        <v>509</v>
       </c>
       <c r="D7" s="7">
-        <v>831</v>
+        <v>700</v>
       </c>
       <c r="E7" s="7">
-        <v>699</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-56</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-7.37</v>
+        <v>494</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-195</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-27.7</v>
       </c>
       <c r="H7" s="9">
-        <v>1.28</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I7" s="8">
-        <v>26.4</v>
-      </c>
-      <c r="J7" s="8">
-        <v>15.8</v>
+        <v>-10.8</v>
+      </c>
+      <c r="J7" s="10">
+        <v>13.2</v>
       </c>
       <c r="K7" s="9">
-        <v>3.56</v>
-      </c>
-      <c r="L7" s="8">
-        <v>14.9</v>
+        <v>4.71</v>
+      </c>
+      <c r="L7" s="10">
+        <v>14.5</v>
       </c>
       <c r="M7" s="9">
-        <v>1.28</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N7" s="8">
-        <v>26.4</v>
-      </c>
-      <c r="O7" s="8">
-        <v>15.8</v>
+        <v>-10.8</v>
+      </c>
+      <c r="O7" s="10">
+        <v>13.2</v>
       </c>
       <c r="P7" s="9">
-        <v>3.56</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>14.9</v>
+        <v>4.71</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>14.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>17</v>
+        <v>44621</v>
+      </c>
+      <c r="B8" s="7">
+        <v>831</v>
+      </c>
+      <c r="C8" s="7">
+        <v>704</v>
+      </c>
+      <c r="D8" s="7">
+        <v>831</v>
+      </c>
+      <c r="E8" s="7">
+        <v>699</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-56</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-7.37</v>
       </c>
       <c r="H8" s="9">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="I8" s="10">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="J8" s="8">
-        <v>12.2</v>
+        <v>26.4</v>
+      </c>
+      <c r="J8" s="10">
+        <v>15.8</v>
       </c>
       <c r="K8" s="9">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="L8" s="8">
-        <v>14.4</v>
+        <v>3.56</v>
+      </c>
+      <c r="L8" s="10">
+        <v>14.9</v>
       </c>
       <c r="M8" s="9">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="N8" s="10">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="O8" s="8">
-        <v>12.2</v>
+        <v>26.4</v>
+      </c>
+      <c r="O8" s="10">
+        <v>15.8</v>
       </c>
       <c r="P8" s="9">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>14.4</v>
+        <v>3.56</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>14.9</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>17</v>
@@ -1616,39 +1616,39 @@
         <v>17</v>
       </c>
       <c r="H9" s="9">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="I9" s="8">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J9" s="8">
-        <v>16.2</v>
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="J9" s="10">
+        <v>12.2</v>
       </c>
       <c r="K9" s="9">
-        <v>1.27</v>
-      </c>
-      <c r="L9" s="8">
-        <v>16.2</v>
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="L9" s="10">
+        <v>14.4</v>
       </c>
       <c r="M9" s="9">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="N9" s="8">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="O9" s="8">
-        <v>16.2</v>
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="O9" s="10">
+        <v>12.2</v>
       </c>
       <c r="P9" s="9">
-        <v>1.27</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>16.2</v>
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>14.4</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>17</v>
@@ -1669,39 +1669,39 @@
         <v>17</v>
       </c>
       <c r="H10" s="9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I10" s="10">
-        <v>-4.17</v>
-      </c>
-      <c r="J10" s="8">
-        <v>33.299999999999997</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J10" s="10">
+        <v>16.2</v>
       </c>
       <c r="K10" s="9">
-        <v>14.07</v>
-      </c>
-      <c r="L10" s="8">
-        <v>37.799999999999997</v>
+        <v>1.27</v>
+      </c>
+      <c r="L10" s="10">
+        <v>16.2</v>
       </c>
       <c r="M10" s="9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="N10" s="10">
-        <v>-4.17</v>
-      </c>
-      <c r="O10" s="8">
-        <v>33.299999999999997</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O10" s="10">
+        <v>16.2</v>
       </c>
       <c r="P10" s="9">
-        <v>14.07</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>37.799999999999997</v>
+        <v>1.27</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>16.2</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>17</v>
@@ -1722,39 +1722,39 @@
         <v>17</v>
       </c>
       <c r="H11" s="9">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="I11" s="8">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="J11" s="8">
-        <v>31.8</v>
+        <v>-4.17</v>
+      </c>
+      <c r="J11" s="10">
+        <v>33.299999999999997</v>
       </c>
       <c r="K11" s="9">
-        <v>12.81</v>
-      </c>
-      <c r="L11" s="8">
-        <v>38.200000000000003</v>
+        <v>14.07</v>
+      </c>
+      <c r="L11" s="10">
+        <v>37.799999999999997</v>
       </c>
       <c r="M11" s="9">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="N11" s="8">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="O11" s="8">
-        <v>31.8</v>
+        <v>-4.17</v>
+      </c>
+      <c r="O11" s="10">
+        <v>33.299999999999997</v>
       </c>
       <c r="P11" s="9">
-        <v>12.81</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>38.200000000000003</v>
+        <v>14.07</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>37.799999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
@@ -1775,39 +1775,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="I12" s="10">
-        <v>-9.64</v>
-      </c>
-      <c r="J12" s="8">
-        <v>27.5</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="J12" s="10">
+        <v>31.8</v>
       </c>
       <c r="K12" s="9">
-        <v>11.49</v>
-      </c>
-      <c r="L12" s="8">
-        <v>39</v>
+        <v>12.81</v>
+      </c>
+      <c r="L12" s="10">
+        <v>38.200000000000003</v>
       </c>
       <c r="M12" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="N12" s="10">
-        <v>-9.64</v>
-      </c>
-      <c r="O12" s="8">
-        <v>27.5</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="O12" s="10">
+        <v>31.8</v>
       </c>
       <c r="P12" s="9">
-        <v>11.49</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>39</v>
+        <v>12.81</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>38.200000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1828,39 +1828,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="I13" s="10">
-        <v>-4.09</v>
-      </c>
-      <c r="J13" s="8">
-        <v>26.7</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-9.64</v>
+      </c>
+      <c r="J13" s="10">
+        <v>27.5</v>
       </c>
       <c r="K13" s="9">
-        <v>10.4</v>
-      </c>
-      <c r="L13" s="8">
-        <v>40.299999999999997</v>
+        <v>11.49</v>
+      </c>
+      <c r="L13" s="10">
+        <v>39</v>
       </c>
       <c r="M13" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="N13" s="10">
-        <v>-4.09</v>
-      </c>
-      <c r="O13" s="8">
-        <v>26.7</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N13" s="8">
+        <v>-9.64</v>
+      </c>
+      <c r="O13" s="10">
+        <v>27.5</v>
       </c>
       <c r="P13" s="9">
-        <v>10.4</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>40.299999999999997</v>
+        <v>11.49</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1881,39 +1881,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
-        <v>1.27</v>
-      </c>
-      <c r="I14" s="10">
-        <v>-1.25</v>
-      </c>
-      <c r="J14" s="8">
-        <v>45.3</v>
+        <v>1.22</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-4.09</v>
+      </c>
+      <c r="J14" s="10">
+        <v>26.7</v>
       </c>
       <c r="K14" s="9">
-        <v>9.18</v>
-      </c>
-      <c r="L14" s="8">
-        <v>42.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="L14" s="10">
+        <v>40.299999999999997</v>
       </c>
       <c r="M14" s="9">
-        <v>1.27</v>
-      </c>
-      <c r="N14" s="10">
-        <v>-1.25</v>
-      </c>
-      <c r="O14" s="8">
-        <v>45.3</v>
+        <v>1.22</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-4.09</v>
+      </c>
+      <c r="O14" s="10">
+        <v>26.7</v>
       </c>
       <c r="P14" s="9">
-        <v>9.18</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>42.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>40.299999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1934,39 +1934,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>1.28</v>
-      </c>
-      <c r="I15" s="10">
-        <v>-1.01</v>
-      </c>
-      <c r="J15" s="8">
-        <v>46.3</v>
+        <v>1.27</v>
+      </c>
+      <c r="I15" s="8">
+        <v>-1.25</v>
+      </c>
+      <c r="J15" s="10">
+        <v>45.3</v>
       </c>
       <c r="K15" s="9">
-        <v>7.91</v>
-      </c>
-      <c r="L15" s="8">
-        <v>41.9</v>
+        <v>9.18</v>
+      </c>
+      <c r="L15" s="10">
+        <v>42.4</v>
       </c>
       <c r="M15" s="9">
-        <v>1.28</v>
-      </c>
-      <c r="N15" s="10">
-        <v>-1.01</v>
-      </c>
-      <c r="O15" s="8">
-        <v>46.3</v>
+        <v>1.27</v>
+      </c>
+      <c r="N15" s="8">
+        <v>-1.25</v>
+      </c>
+      <c r="O15" s="10">
+        <v>45.3</v>
       </c>
       <c r="P15" s="9">
-        <v>7.91</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>41.9</v>
+        <v>9.18</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>42.4</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1987,39 +1987,39 @@
         <v>17</v>
       </c>
       <c r="H16" s="9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="I16" s="8">
-        <v>6.33</v>
-      </c>
-      <c r="J16" s="8">
-        <v>53.3</v>
+        <v>-1.01</v>
+      </c>
+      <c r="J16" s="10">
+        <v>46.3</v>
       </c>
       <c r="K16" s="9">
-        <v>6.63</v>
-      </c>
-      <c r="L16" s="8">
-        <v>41.1</v>
+        <v>7.91</v>
+      </c>
+      <c r="L16" s="10">
+        <v>41.9</v>
       </c>
       <c r="M16" s="9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="N16" s="8">
-        <v>6.33</v>
-      </c>
-      <c r="O16" s="8">
-        <v>53.3</v>
+        <v>-1.01</v>
+      </c>
+      <c r="O16" s="10">
+        <v>46.3</v>
       </c>
       <c r="P16" s="9">
-        <v>6.63</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>41.1</v>
+        <v>7.91</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>41.9</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2040,39 +2040,39 @@
         <v>17</v>
       </c>
       <c r="H17" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="I17" s="8">
-        <v>12</v>
-      </c>
-      <c r="J17" s="8">
-        <v>42.4</v>
+        <v>1.3</v>
+      </c>
+      <c r="I17" s="10">
+        <v>6.33</v>
+      </c>
+      <c r="J17" s="10">
+        <v>53.3</v>
       </c>
       <c r="K17" s="9">
-        <v>5.33</v>
-      </c>
-      <c r="L17" s="8">
-        <v>25.3</v>
+        <v>6.63</v>
+      </c>
+      <c r="L17" s="10">
+        <v>41.1</v>
       </c>
       <c r="M17" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="N17" s="8">
-        <v>12</v>
-      </c>
-      <c r="O17" s="8">
-        <v>42.4</v>
+        <v>1.3</v>
+      </c>
+      <c r="N17" s="10">
+        <v>6.33</v>
+      </c>
+      <c r="O17" s="10">
+        <v>53.3</v>
       </c>
       <c r="P17" s="9">
-        <v>5.33</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>25.3</v>
+        <v>6.63</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>41.1</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2093,39 +2093,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="9">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="I18" s="10">
-        <v>-15.8</v>
-      </c>
-      <c r="J18" s="8">
-        <v>17.7</v>
+        <v>12</v>
+      </c>
+      <c r="J18" s="10">
+        <v>42.4</v>
       </c>
       <c r="K18" s="9">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="L18" s="8">
-        <v>21</v>
+        <v>5.33</v>
+      </c>
+      <c r="L18" s="10">
+        <v>25.3</v>
       </c>
       <c r="M18" s="9">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="N18" s="10">
-        <v>-15.8</v>
-      </c>
-      <c r="O18" s="8">
-        <v>17.7</v>
+        <v>12</v>
+      </c>
+      <c r="O18" s="10">
+        <v>42.4</v>
       </c>
       <c r="P18" s="9">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>21</v>
+        <v>5.33</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>25.3</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2146,39 +2146,39 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
-        <v>1.1100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="I19" s="8">
-        <v>11.7</v>
-      </c>
-      <c r="J19" s="8">
-        <v>21.2</v>
+        <v>-15.8</v>
+      </c>
+      <c r="J19" s="10">
+        <v>17.7</v>
       </c>
       <c r="K19" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="L19" s="8">
-        <v>22.2</v>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="L19" s="10">
+        <v>21</v>
       </c>
       <c r="M19" s="9">
-        <v>1.1100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="N19" s="8">
-        <v>11.7</v>
-      </c>
-      <c r="O19" s="8">
-        <v>21.2</v>
+        <v>-15.8</v>
+      </c>
+      <c r="O19" s="10">
+        <v>17.7</v>
       </c>
       <c r="P19" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>22.2</v>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2199,39 +2199,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="9">
-        <v>0.90400000000000003</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I20" s="10">
-        <v>-22.9</v>
-      </c>
-      <c r="J20" s="8">
-        <v>14.7</v>
+        <v>11.7</v>
+      </c>
+      <c r="J20" s="10">
+        <v>21.2</v>
       </c>
       <c r="K20" s="9">
-        <v>1.99</v>
-      </c>
-      <c r="L20" s="8">
-        <v>22.7</v>
+        <v>3.1</v>
+      </c>
+      <c r="L20" s="10">
+        <v>22.2</v>
       </c>
       <c r="M20" s="9">
-        <v>0.90400000000000003</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N20" s="10">
-        <v>-22.9</v>
-      </c>
-      <c r="O20" s="8">
-        <v>14.7</v>
+        <v>11.7</v>
+      </c>
+      <c r="O20" s="10">
+        <v>21.2</v>
       </c>
       <c r="P20" s="9">
-        <v>1.99</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>22.7</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>22.2</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2252,39 +2252,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="9">
-        <v>1.0900000000000001</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="I21" s="8">
-        <v>5.04</v>
-      </c>
-      <c r="J21" s="8">
-        <v>30.2</v>
+        <v>-22.9</v>
+      </c>
+      <c r="J21" s="10">
+        <v>14.7</v>
       </c>
       <c r="K21" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="L21" s="8">
-        <v>30.2</v>
+        <v>1.99</v>
+      </c>
+      <c r="L21" s="10">
+        <v>22.7</v>
       </c>
       <c r="M21" s="9">
-        <v>1.0900000000000001</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="N21" s="8">
-        <v>5.04</v>
-      </c>
-      <c r="O21" s="8">
-        <v>30.2</v>
+        <v>-22.9</v>
+      </c>
+      <c r="O21" s="10">
+        <v>14.7</v>
       </c>
       <c r="P21" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>30.2</v>
+        <v>1.99</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>22.7</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2305,39 +2305,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="9">
-        <v>0.94399999999999995</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I22" s="10">
-        <v>-12.5</v>
-      </c>
-      <c r="J22" s="8">
-        <v>9.3800000000000008</v>
+        <v>5.04</v>
+      </c>
+      <c r="J22" s="10">
+        <v>30.2</v>
       </c>
       <c r="K22" s="9">
-        <v>10.210000000000001</v>
-      </c>
-      <c r="L22" s="8">
-        <v>9.07</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="L22" s="10">
+        <v>30.2</v>
       </c>
       <c r="M22" s="9">
-        <v>0.94399999999999995</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N22" s="10">
-        <v>-12.5</v>
-      </c>
-      <c r="O22" s="8">
-        <v>9.3800000000000008</v>
+        <v>5.04</v>
+      </c>
+      <c r="O22" s="10">
+        <v>30.2</v>
       </c>
       <c r="P22" s="9">
-        <v>10.210000000000001</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>9.07</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>30.2</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2358,39 +2358,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="9">
-        <v>0.997</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="I23" s="8">
-        <v>6.16</v>
-      </c>
-      <c r="J23" s="8">
-        <v>21.6</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J23" s="10">
+        <v>9.3800000000000008</v>
       </c>
       <c r="K23" s="9">
-        <v>9.27</v>
-      </c>
-      <c r="L23" s="8">
-        <v>9.0399999999999991</v>
+        <v>10.210000000000001</v>
+      </c>
+      <c r="L23" s="10">
+        <v>9.07</v>
       </c>
       <c r="M23" s="9">
-        <v>0.997</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="N23" s="8">
-        <v>6.16</v>
-      </c>
-      <c r="O23" s="8">
-        <v>21.6</v>
+        <v>-12.5</v>
+      </c>
+      <c r="O23" s="10">
+        <v>9.3800000000000008</v>
       </c>
       <c r="P23" s="9">
-        <v>9.27</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>9.0399999999999991</v>
+        <v>10.210000000000001</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>9.07</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>17</v>
@@ -2411,39 +2411,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="9">
-        <v>0.86199999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="I24" s="10">
-        <v>-18</v>
-      </c>
-      <c r="J24" s="8">
-        <v>3.68</v>
+        <v>6.16</v>
+      </c>
+      <c r="J24" s="10">
+        <v>21.6</v>
       </c>
       <c r="K24" s="9">
-        <v>8.27</v>
-      </c>
-      <c r="L24" s="8">
-        <v>7.7</v>
+        <v>9.27</v>
+      </c>
+      <c r="L24" s="10">
+        <v>9.0399999999999991</v>
       </c>
       <c r="M24" s="9">
-        <v>0.86199999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="N24" s="10">
-        <v>-18</v>
-      </c>
-      <c r="O24" s="8">
-        <v>3.68</v>
+        <v>6.16</v>
+      </c>
+      <c r="O24" s="10">
+        <v>21.6</v>
       </c>
       <c r="P24" s="9">
-        <v>8.27</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>7.7</v>
+        <v>9.27</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>9.0399999999999991</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>17</v>
@@ -2464,39 +2464,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="9">
-        <v>0.95899999999999996</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="I25" s="8">
-        <v>0.97</v>
-      </c>
-      <c r="J25" s="8">
-        <v>23.5</v>
+        <v>-18</v>
+      </c>
+      <c r="J25" s="10">
+        <v>3.68</v>
       </c>
       <c r="K25" s="9">
-        <v>7.41</v>
-      </c>
-      <c r="L25" s="8">
-        <v>8.19</v>
+        <v>8.27</v>
+      </c>
+      <c r="L25" s="10">
+        <v>7.7</v>
       </c>
       <c r="M25" s="9">
-        <v>0.95899999999999996</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="N25" s="8">
-        <v>0.97</v>
-      </c>
-      <c r="O25" s="8">
-        <v>23.5</v>
+        <v>-18</v>
+      </c>
+      <c r="O25" s="10">
+        <v>3.68</v>
       </c>
       <c r="P25" s="9">
-        <v>7.41</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>8.19</v>
+        <v>8.27</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>7.7</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2517,39 +2517,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>0.872</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="I26" s="10">
-        <v>-9.3800000000000008</v>
-      </c>
-      <c r="J26" s="8">
-        <v>14.3</v>
+        <v>0.97</v>
+      </c>
+      <c r="J26" s="10">
+        <v>23.5</v>
       </c>
       <c r="K26" s="9">
-        <v>6.45</v>
-      </c>
-      <c r="L26" s="8">
-        <v>6.23</v>
+        <v>7.41</v>
+      </c>
+      <c r="L26" s="10">
+        <v>8.19</v>
       </c>
       <c r="M26" s="9">
-        <v>0.872</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="N26" s="10">
-        <v>-9.3800000000000008</v>
-      </c>
-      <c r="O26" s="8">
-        <v>14.3</v>
+        <v>0.97</v>
+      </c>
+      <c r="O26" s="10">
+        <v>23.5</v>
       </c>
       <c r="P26" s="9">
-        <v>6.45</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>6.23</v>
+        <v>7.41</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>8.19</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2570,39 +2570,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>0.877</v>
-      </c>
-      <c r="I27" s="10">
-        <v>-5.41</v>
-      </c>
-      <c r="J27" s="8">
-        <v>5.67</v>
+        <v>0.872</v>
+      </c>
+      <c r="I27" s="8">
+        <v>-9.3800000000000008</v>
+      </c>
+      <c r="J27" s="10">
+        <v>14.3</v>
       </c>
       <c r="K27" s="9">
-        <v>5.58</v>
-      </c>
-      <c r="L27" s="8">
-        <v>5.07</v>
+        <v>6.45</v>
+      </c>
+      <c r="L27" s="10">
+        <v>6.23</v>
       </c>
       <c r="M27" s="9">
-        <v>0.877</v>
-      </c>
-      <c r="N27" s="10">
-        <v>-5.41</v>
-      </c>
-      <c r="O27" s="8">
-        <v>5.67</v>
+        <v>0.872</v>
+      </c>
+      <c r="N27" s="8">
+        <v>-9.3800000000000008</v>
+      </c>
+      <c r="O27" s="10">
+        <v>14.3</v>
       </c>
       <c r="P27" s="9">
-        <v>5.58</v>
-      </c>
-      <c r="Q27" s="8">
-        <v>5.07</v>
+        <v>6.45</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>6.23</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2623,39 +2623,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="I28" s="10">
-        <v>-1.26</v>
-      </c>
-      <c r="J28" s="8">
-        <v>19</v>
+        <v>0.877</v>
+      </c>
+      <c r="I28" s="8">
+        <v>-5.41</v>
+      </c>
+      <c r="J28" s="10">
+        <v>5.67</v>
       </c>
       <c r="K28" s="9">
-        <v>4.7</v>
-      </c>
-      <c r="L28" s="8">
-        <v>4.96</v>
+        <v>5.58</v>
+      </c>
+      <c r="L28" s="10">
+        <v>5.07</v>
       </c>
       <c r="M28" s="9">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="N28" s="10">
-        <v>-1.26</v>
-      </c>
-      <c r="O28" s="8">
-        <v>19</v>
+        <v>0.877</v>
+      </c>
+      <c r="N28" s="8">
+        <v>-5.41</v>
+      </c>
+      <c r="O28" s="10">
+        <v>5.67</v>
       </c>
       <c r="P28" s="9">
-        <v>4.7</v>
-      </c>
-      <c r="Q28" s="8">
-        <v>4.96</v>
+        <v>5.58</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>5.07</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2676,39 +2676,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="9">
-        <v>0.85699999999999998</v>
-      </c>
-      <c r="I29" s="10">
-        <v>-0.31</v>
-      </c>
-      <c r="J29" s="8">
-        <v>6.72</v>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="I29" s="8">
+        <v>-1.26</v>
+      </c>
+      <c r="J29" s="10">
+        <v>19</v>
       </c>
       <c r="K29" s="9">
-        <v>4.26</v>
-      </c>
-      <c r="L29" s="8">
-        <v>13</v>
+        <v>4.7</v>
+      </c>
+      <c r="L29" s="10">
+        <v>4.96</v>
       </c>
       <c r="M29" s="9">
-        <v>0.85699999999999998</v>
-      </c>
-      <c r="N29" s="10">
-        <v>-0.31</v>
-      </c>
-      <c r="O29" s="8">
-        <v>6.72</v>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="N29" s="8">
+        <v>-1.26</v>
+      </c>
+      <c r="O29" s="10">
+        <v>19</v>
       </c>
       <c r="P29" s="9">
-        <v>4.26</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>13</v>
+        <v>4.7</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>4.96</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2729,39 +2729,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="9">
-        <v>0.85899999999999999</v>
-      </c>
-      <c r="I30" s="10">
-        <v>-6.01</v>
-      </c>
-      <c r="J30" s="8">
-        <v>7.58</v>
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="I30" s="8">
+        <v>-0.31</v>
+      </c>
+      <c r="J30" s="10">
+        <v>6.72</v>
       </c>
       <c r="K30" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="L30" s="8">
-        <v>14.7</v>
+        <v>4.26</v>
+      </c>
+      <c r="L30" s="10">
+        <v>13</v>
       </c>
       <c r="M30" s="9">
-        <v>0.85899999999999999</v>
-      </c>
-      <c r="N30" s="10">
-        <v>-6.01</v>
-      </c>
-      <c r="O30" s="8">
-        <v>7.58</v>
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="N30" s="8">
+        <v>-0.31</v>
+      </c>
+      <c r="O30" s="10">
+        <v>6.72</v>
       </c>
       <c r="P30" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="Q30" s="8">
-        <v>14.7</v>
+        <v>4.26</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2782,39 +2782,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="9">
-        <v>0.91400000000000003</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="I31" s="8">
-        <v>16</v>
-      </c>
-      <c r="J31" s="8">
-        <v>21.6</v>
+        <v>-6.01</v>
+      </c>
+      <c r="J31" s="10">
+        <v>7.58</v>
       </c>
       <c r="K31" s="9">
-        <v>2.54</v>
-      </c>
-      <c r="L31" s="8">
-        <v>17.3</v>
+        <v>3.4</v>
+      </c>
+      <c r="L31" s="10">
+        <v>14.7</v>
       </c>
       <c r="M31" s="9">
-        <v>0.91400000000000003</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="N31" s="8">
-        <v>16</v>
-      </c>
-      <c r="O31" s="8">
-        <v>21.6</v>
+        <v>-6.01</v>
+      </c>
+      <c r="O31" s="10">
+        <v>7.58</v>
       </c>
       <c r="P31" s="9">
-        <v>2.54</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>17.3</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>14.7</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2835,39 +2835,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="9">
-        <v>0.78800000000000003</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="I32" s="10">
-        <v>-5.79</v>
-      </c>
-      <c r="J32" s="8">
-        <v>28.6</v>
+        <v>16</v>
+      </c>
+      <c r="J32" s="10">
+        <v>21.6</v>
       </c>
       <c r="K32" s="9">
-        <v>1.63</v>
-      </c>
-      <c r="L32" s="8">
-        <v>15</v>
+        <v>2.54</v>
+      </c>
+      <c r="L32" s="10">
+        <v>17.3</v>
       </c>
       <c r="M32" s="9">
-        <v>0.78800000000000003</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="N32" s="10">
-        <v>-5.79</v>
-      </c>
-      <c r="O32" s="8">
-        <v>28.6</v>
+        <v>16</v>
+      </c>
+      <c r="O32" s="10">
+        <v>21.6</v>
       </c>
       <c r="P32" s="9">
-        <v>1.63</v>
-      </c>
-      <c r="Q32" s="8">
-        <v>15</v>
+        <v>2.54</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>17.3</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2888,39 +2888,39 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="I33" s="10">
-        <v>-3.08</v>
-      </c>
-      <c r="J33" s="8">
-        <v>4.59</v>
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="I33" s="8">
+        <v>-5.79</v>
+      </c>
+      <c r="J33" s="10">
+        <v>28.6</v>
       </c>
       <c r="K33" s="9">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="L33" s="8">
-        <v>4.59</v>
+        <v>1.63</v>
+      </c>
+      <c r="L33" s="10">
+        <v>15</v>
       </c>
       <c r="M33" s="9">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="N33" s="10">
-        <v>-3.08</v>
-      </c>
-      <c r="O33" s="8">
-        <v>4.59</v>
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="N33" s="8">
+        <v>-5.79</v>
+      </c>
+      <c r="O33" s="10">
+        <v>28.6</v>
       </c>
       <c r="P33" s="9">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>4.59</v>
+        <v>1.63</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2941,39 +2941,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="9">
-        <v>0.86399999999999999</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="I34" s="8">
-        <v>5.32</v>
-      </c>
-      <c r="J34" s="8">
-        <v>39.799999999999997</v>
+        <v>-3.08</v>
+      </c>
+      <c r="J34" s="10">
+        <v>4.59</v>
       </c>
       <c r="K34" s="9">
-        <v>9.36</v>
-      </c>
-      <c r="L34" s="8">
-        <v>47.6</v>
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="L34" s="10">
+        <v>4.59</v>
       </c>
       <c r="M34" s="9">
-        <v>0.86399999999999999</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="N34" s="8">
-        <v>5.32</v>
-      </c>
-      <c r="O34" s="8">
-        <v>39.799999999999997</v>
+        <v>-3.08</v>
+      </c>
+      <c r="O34" s="10">
+        <v>4.59</v>
       </c>
       <c r="P34" s="9">
-        <v>9.36</v>
-      </c>
-      <c r="Q34" s="8">
-        <v>47.6</v>
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="Q34" s="10">
+        <v>4.59</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2994,39 +2994,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="9">
-        <v>0.82</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="I35" s="10">
-        <v>-1.32</v>
-      </c>
-      <c r="J35" s="8">
-        <v>25.8</v>
+        <v>5.32</v>
+      </c>
+      <c r="J35" s="10">
+        <v>39.799999999999997</v>
       </c>
       <c r="K35" s="9">
-        <v>8.5</v>
-      </c>
-      <c r="L35" s="8">
-        <v>48.4</v>
+        <v>9.36</v>
+      </c>
+      <c r="L35" s="10">
+        <v>47.6</v>
       </c>
       <c r="M35" s="9">
-        <v>0.82</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="N35" s="10">
-        <v>-1.32</v>
-      </c>
-      <c r="O35" s="8">
-        <v>25.8</v>
+        <v>5.32</v>
+      </c>
+      <c r="O35" s="10">
+        <v>39.799999999999997</v>
       </c>
       <c r="P35" s="9">
-        <v>8.5</v>
-      </c>
-      <c r="Q35" s="8">
-        <v>48.4</v>
+        <v>9.36</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>47.6</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3047,86 +3047,139 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>0.83099999999999996</v>
+        <v>0.82</v>
       </c>
       <c r="I36" s="8">
-        <v>6.98</v>
-      </c>
-      <c r="J36" s="8">
-        <v>32.4</v>
+        <v>-1.32</v>
+      </c>
+      <c r="J36" s="10">
+        <v>25.8</v>
       </c>
       <c r="K36" s="9">
-        <v>7.68</v>
-      </c>
-      <c r="L36" s="8">
-        <v>51.3</v>
+        <v>8.5</v>
+      </c>
+      <c r="L36" s="10">
+        <v>48.4</v>
       </c>
       <c r="M36" s="9">
-        <v>0.83099999999999996</v>
+        <v>0.82</v>
       </c>
       <c r="N36" s="8">
-        <v>6.98</v>
-      </c>
-      <c r="O36" s="8">
-        <v>32.4</v>
+        <v>-1.32</v>
+      </c>
+      <c r="O36" s="10">
+        <v>25.8</v>
       </c>
       <c r="P36" s="9">
-        <v>7.68</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>51.3</v>
+        <v>8.5</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>48.4</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
+        <v>43739</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="9">
+        <v>0.83099999999999996</v>
+      </c>
+      <c r="I37" s="10">
+        <v>6.98</v>
+      </c>
+      <c r="J37" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="K37" s="9">
+        <v>7.68</v>
+      </c>
+      <c r="L37" s="10">
+        <v>51.3</v>
+      </c>
+      <c r="M37" s="9">
+        <v>0.83099999999999996</v>
+      </c>
+      <c r="N37" s="10">
+        <v>6.98</v>
+      </c>
+      <c r="O37" s="10">
+        <v>32.4</v>
+      </c>
+      <c r="P37" s="9">
+        <v>7.68</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
         <v>43709</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="9">
+      <c r="B38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="9">
         <v>0.77700000000000002</v>
       </c>
-      <c r="I37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="8">
+      <c r="I38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="10">
         <v>42.8</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K38" s="9">
         <v>6.85</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L38" s="10">
         <v>54</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M38" s="9">
         <v>0.77700000000000002</v>
       </c>
-      <c r="N37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O37" s="8">
+      <c r="N38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O38" s="10">
         <v>42.8</v>
       </c>
-      <c r="P37" s="9">
+      <c r="P38" s="9">
         <v>6.85</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="Q38" s="10">
         <v>54</v>
       </c>
     </row>
